--- a/Excel/一方通行/测试N.xlsx
+++ b/Excel/一方通行/测试N.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B560246-A2DA-4829-924E-973C6C47E2AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1CD8EA-981E-4588-9363-8988B0E213C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4390" uniqueCount="1650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4391" uniqueCount="1655">
   <si>
     <t>Id</t>
   </si>
@@ -5384,6 +5384,21 @@
   <si>
     <t>token_10054_phatm2_encdool</t>
     <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
+    <t>char_1040_blaze2</t>
+  </si>
+  <si>
+    <t>char_4204_mantra</t>
+  </si>
+  <si>
+    <t>char_1013_chen2</t>
+  </si>
+  <si>
+    <t>char_4193_lemuen</t>
+  </si>
+  <si>
+    <t>char_1035_wisdel</t>
   </si>
 </sst>
 </file>
@@ -8868,7 +8883,7 @@
         <v>245</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>11</v>
+        <v>1650</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -8998,7 +9013,7 @@
       </c>
       <c r="E21" s="32"/>
       <c r="F21" s="1" t="s">
-        <v>12</v>
+        <v>1651</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -9268,7 +9283,7 @@
         <v>259</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>260</v>
+        <v>1652</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -9402,7 +9417,7 @@
         <v>4193</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>15</v>
+        <v>1653</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -9542,7 +9557,7 @@
         <v>273</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>16</v>
+        <v>1654</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -9685,7 +9700,7 @@
         <v>1035</v>
       </c>
       <c r="F26" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -31423,6 +31438,9 @@
       <c r="AC338">
         <v>1</v>
       </c>
+      <c r="AT338" t="s">
+        <v>1191</v>
+      </c>
       <c r="BD338">
         <v>1</v>
       </c>

--- a/Excel/一方通行/测试N.xlsx
+++ b/Excel/一方通行/测试N.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1CD8EA-981E-4588-9363-8988B0E213C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC964A45-BCAE-42D7-97F5-9BD9D628D13A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4391" uniqueCount="1655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4391" uniqueCount="1656">
   <si>
     <t>Id</t>
   </si>
@@ -5399,6 +5399,10 @@
   </si>
   <si>
     <t>char_1035_wisdel</t>
+  </si>
+  <si>
+    <t>0,1#0,-1#1,0#2,0#1,1#1,-1#2,1#2,-1#3,0#3,1#3,-1#0,2#0,-2#1,2#1,-2#2,2#2,-2#4,0</t>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -30015,8 +30019,8 @@
       <c r="AC315">
         <v>1</v>
       </c>
-      <c r="AT315" t="s">
-        <v>1191</v>
+      <c r="AT315" s="41" t="s">
+        <v>1655</v>
       </c>
       <c r="BD315">
         <v>1</v>
@@ -31438,8 +31442,8 @@
       <c r="AC338">
         <v>1</v>
       </c>
-      <c r="AT338" t="s">
-        <v>1191</v>
+      <c r="AT338" s="41" t="s">
+        <v>1655</v>
       </c>
       <c r="BD338">
         <v>1</v>

--- a/Excel/一方通行/测试N.xlsx
+++ b/Excel/一方通行/测试N.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC964A45-BCAE-42D7-97F5-9BD9D628D13A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9582B677-F9C2-4797-BBF2-88B34BAB238E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
